--- a/01 - excel-mysql-incremental-etl/dados_brutos.xlsx
+++ b/01 - excel-mysql-incremental-etl/dados_brutos.xlsx
@@ -5,15 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\mateus\Estudos\Privado-main\Privado-main\Portifolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateu\Desktop\Portfolio\01 - excel-mysql-incremental-etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0272B8C5-C0E2-4706-B335-1CB1D8095497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD2B83-8A11-40D7-A72C-D35E11C74140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{19E6D628-E50E-4A3F-BBCD-D078513A6FB2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{19E6D628-E50E-4A3F-BBCD-D078513A6FB2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="dim_produto" sheetId="1" r:id="rId1"/>
+    <sheet name="dim_loja" sheetId="3" r:id="rId2"/>
+    <sheet name="dim_cliente" sheetId="4" r:id="rId3"/>
+    <sheet name="fato_vendas" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,22 +28,97 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>id_produto</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>nome_produto</t>
   </si>
   <si>
     <t>categoria</t>
   </si>
+  <si>
+    <t>Microfone</t>
+  </si>
+  <si>
+    <t>Utilitário</t>
+  </si>
+  <si>
+    <t>preco_producao</t>
+  </si>
+  <si>
+    <t>preco_venda</t>
+  </si>
+  <si>
+    <t>nome_loja</t>
+  </si>
+  <si>
+    <t>tipo_loja</t>
+  </si>
+  <si>
+    <t>gerente_loja</t>
+  </si>
+  <si>
+    <t>cpf_cliente</t>
+  </si>
+  <si>
+    <t>cidade</t>
+  </si>
+  <si>
+    <t>data_cadastro</t>
+  </si>
+  <si>
+    <t>data_venda</t>
+  </si>
+  <si>
+    <t>quantidade</t>
+  </si>
+  <si>
+    <t>valor_total</t>
+  </si>
+  <si>
+    <t>Física</t>
+  </si>
+  <si>
+    <t>Rian</t>
+  </si>
+  <si>
+    <t>LinuXIAN</t>
+  </si>
+  <si>
+    <t>Yago</t>
+  </si>
+  <si>
+    <t>67ech</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Felipe</t>
+  </si>
+  <si>
+    <t>Caçapava</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>nome_cliente</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>valor_unitario</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +146,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -111,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -123,6 +216,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,424 +547,2250 @@
   <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="23.33203125" customWidth="1"/>
+    <col min="1" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="4" width="23.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>150</v>
+      </c>
+      <c r="D2" s="5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+    </row>
+    <row r="46" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+    </row>
+    <row r="48" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+    </row>
+    <row r="49" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+    </row>
+    <row r="50" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+    </row>
+    <row r="51" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+    </row>
+    <row r="53" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+    </row>
+    <row r="57" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+    </row>
+    <row r="59" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+    </row>
+    <row r="60" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+    </row>
+    <row r="61" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+    </row>
+    <row r="62" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+    </row>
+    <row r="64" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+    </row>
+    <row r="65" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+    </row>
+    <row r="68" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+    </row>
+    <row r="69" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+    </row>
+    <row r="70" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+    </row>
+    <row r="71" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+    </row>
+    <row r="72" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+    </row>
+    <row r="73" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+    </row>
+    <row r="74" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+    </row>
+    <row r="75" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+    </row>
+    <row r="76" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+    </row>
+    <row r="77" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+    </row>
+    <row r="78" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+    </row>
+    <row r="79" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+    </row>
+    <row r="80" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+    </row>
+    <row r="81" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CD50CD-4979-4707-AA0D-1607189C7FED}">
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="6" customWidth="1"/>
+    <col min="4" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D1"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="5"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="5"/>
+    </row>
+    <row r="22" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="5"/>
+    </row>
+    <row r="33" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="5"/>
+    </row>
+    <row r="34" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="5"/>
+    </row>
+    <row r="35" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="5"/>
+    </row>
+    <row r="36" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="5"/>
+    </row>
+    <row r="37" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="5"/>
+    </row>
+    <row r="38" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="5"/>
+    </row>
+    <row r="39" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="5"/>
+    </row>
+    <row r="40" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="5"/>
+    </row>
+    <row r="43" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="5"/>
+    </row>
+    <row r="44" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="5"/>
+    </row>
+    <row r="45" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="5"/>
+    </row>
+    <row r="46" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="5"/>
+    </row>
+    <row r="47" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="5"/>
+    </row>
+    <row r="48" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="5"/>
+    </row>
+    <row r="49" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="5"/>
+    </row>
+    <row r="51" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="5"/>
+    </row>
+    <row r="52" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="5"/>
+    </row>
+    <row r="53" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="5"/>
+    </row>
+    <row r="54" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="5"/>
+    </row>
+    <row r="55" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="5"/>
+    </row>
+    <row r="56" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="5"/>
+    </row>
+    <row r="57" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="5"/>
+    </row>
+    <row r="58" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="5"/>
+    </row>
+    <row r="59" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="5"/>
+    </row>
+    <row r="60" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="5"/>
+    </row>
+    <row r="61" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="5"/>
+    </row>
+    <row r="62" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="5"/>
+    </row>
+    <row r="63" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="5"/>
+    </row>
+    <row r="64" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="5"/>
+    </row>
+    <row r="65" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="5"/>
+    </row>
+    <row r="66" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="5"/>
+    </row>
+    <row r="67" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="5"/>
+    </row>
+    <row r="68" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="5"/>
+    </row>
+    <row r="69" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="5"/>
+    </row>
+    <row r="70" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="5"/>
+    </row>
+    <row r="71" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="5"/>
+    </row>
+    <row r="72" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="5"/>
+    </row>
+    <row r="73" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="5"/>
+    </row>
+    <row r="74" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="5"/>
+    </row>
+    <row r="75" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="5"/>
+    </row>
+    <row r="76" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="5"/>
+    </row>
+    <row r="77" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="5"/>
+    </row>
+    <row r="78" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="5"/>
+    </row>
+    <row r="79" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="5"/>
+    </row>
+    <row r="80" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="5"/>
+    </row>
+    <row r="81" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C59B78A-DC26-4531-A1DD-42F92E257883}">
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>54221278901</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="7">
+        <v>46325</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="E4" s="4"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="2"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="2"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="2"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="2"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="2"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="2"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D24" s="2"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D25" s="2"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="2"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="2"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="2"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="2"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="2"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="2"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="2"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="2"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="2"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="2"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="2"/>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="2"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="2"/>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="2"/>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="2"/>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="2"/>
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="2"/>
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D43" s="2"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D44" s="2"/>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D45" s="2"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D46" s="2"/>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D47" s="2"/>
+      <c r="E47" s="7"/>
+    </row>
+    <row r="48" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="2"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D49" s="2"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D50" s="2"/>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D51" s="2"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="2"/>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D53" s="2"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D54" s="2"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D55" s="2"/>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="2"/>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="2"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D58" s="2"/>
+      <c r="E58" s="7"/>
+    </row>
+    <row r="59" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D59" s="2"/>
+      <c r="E59" s="7"/>
+    </row>
+    <row r="60" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D60" s="2"/>
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-    </row>
-    <row r="62" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D61" s="2"/>
+      <c r="E61" s="7"/>
+    </row>
+    <row r="62" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D62" s="2"/>
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D63" s="2"/>
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D64" s="2"/>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D65" s="2"/>
+      <c r="E65" s="7"/>
+    </row>
+    <row r="66" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-    </row>
-    <row r="67" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="2"/>
+      <c r="E66" s="7"/>
+    </row>
+    <row r="67" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-    </row>
-    <row r="68" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="2"/>
+      <c r="E67" s="7"/>
+    </row>
+    <row r="68" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-    </row>
-    <row r="69" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="2"/>
+      <c r="E68" s="7"/>
+    </row>
+    <row r="69" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-    </row>
-    <row r="70" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="2"/>
+      <c r="E69" s="7"/>
+    </row>
+    <row r="70" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-    </row>
-    <row r="71" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="2"/>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="2"/>
+      <c r="E71" s="7"/>
+    </row>
+    <row r="72" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-    </row>
-    <row r="73" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="2"/>
+      <c r="E72" s="7"/>
+    </row>
+    <row r="73" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-    </row>
-    <row r="74" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="2"/>
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-    </row>
-    <row r="75" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="2"/>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-    </row>
-    <row r="76" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="2"/>
+      <c r="E75" s="7"/>
+    </row>
+    <row r="76" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-    </row>
-    <row r="77" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D76" s="2"/>
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
-    </row>
-    <row r="78" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D77" s="2"/>
+      <c r="E77" s="7"/>
+    </row>
+    <row r="78" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-    </row>
-    <row r="79" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D78" s="2"/>
+      <c r="E78" s="7"/>
+    </row>
+    <row r="79" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-    </row>
-    <row r="80" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D79" s="2"/>
+      <c r="E79" s="7"/>
+    </row>
+    <row r="80" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-    </row>
-    <row r="81" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D80" s="2"/>
+      <c r="E80" s="7"/>
+    </row>
+    <row r="81" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4C58169-2DA1-46BA-BC8A-38444E6E736B}">
+  <dimension ref="A1:N81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="6" width="23.33203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>46325</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
+        <v>54221278901</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5">
+        <v>150</v>
+      </c>
+      <c r="F2" s="5">
+        <f>D2*E2</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="I6" s="4"/>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+    </row>
+    <row r="41" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+    </row>
+    <row r="44" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+    </row>
+    <row r="46" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+    </row>
+    <row r="48" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+    </row>
+    <row r="52" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+    </row>
+    <row r="53" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+    </row>
+    <row r="54" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+    </row>
+    <row r="55" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+    </row>
+    <row r="56" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+    </row>
+    <row r="59" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+    </row>
+    <row r="60" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+    </row>
+    <row r="61" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+    </row>
+    <row r="62" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+    </row>
+    <row r="63" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+    </row>
+    <row r="64" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+    </row>
+    <row r="65" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+    </row>
+    <row r="66" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+    </row>
+    <row r="67" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+    </row>
+    <row r="68" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+    </row>
+    <row r="69" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+    </row>
+    <row r="70" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+    </row>
+    <row r="71" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+    </row>
+    <row r="72" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+    </row>
+    <row r="73" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+    </row>
+    <row r="74" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+    </row>
+    <row r="75" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+    </row>
+    <row r="76" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+    </row>
+    <row r="77" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+    </row>
+    <row r="78" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+    </row>
+    <row r="79" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+    </row>
+    <row r="80" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+    </row>
+    <row r="81" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>